--- a/data/indicadores/05_01_01_01_pga.xlsx
+++ b/data/indicadores/05_01_01_01_pga.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Paolo\Desktop\ods_paolo\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SDSN\Atlas2025\R_codes\Final\Input_indicadores\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{81326AC2-B4D3-446C-B8B4-7E22DE49CEC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48DF565F-AB69-479E-9F6E-A978033AB1D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos Procesados" sheetId="1" r:id="rId1"/>
@@ -1531,6 +1531,7 @@
     <font>
       <sz val="8"/>
       <name val="Arial"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -63083,28 +63084,28 @@
       <c r="B2" s="28" t="s">
         <v>474</v>
       </c>
-      <c r="C2" s="33">
+      <c r="C2">
+        <v>8</v>
+      </c>
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="D2" s="33">
+      <c r="E2">
         <v>1</v>
       </c>
-      <c r="E2" s="33">
-        <v>1</v>
-      </c>
-      <c r="F2" s="33">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="G2" s="33">
-        <v>0.86499999999999999</v>
-      </c>
-      <c r="H2" s="33">
-        <v>0.73</v>
-      </c>
-      <c r="I2" s="33">
-        <v>0.73</v>
-      </c>
-      <c r="J2" s="33">
+      <c r="F2">
+        <v>0.75</v>
+      </c>
+      <c r="G2">
+        <v>0.75</v>
+      </c>
+      <c r="H2">
+        <v>0.5</v>
+      </c>
+      <c r="I2">
+        <v>0.5</v>
+      </c>
+      <c r="J2">
         <v>0</v>
       </c>
       <c r="K2" s="16"/>
